--- a/database excel/daybook_records.xlsx
+++ b/database excel/daybook_records.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Employees" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LeaveRequests" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balances" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PolicyDates" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ActivityEvents" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Employees" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="LeaveRequests" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Decisions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Balances" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="PolicyDates" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ActivityEvents" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:52</t>
+          <t>2026-06-21T14:46:26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:52</t>
+          <t>2026-06-21T14:46:27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -558,7 +558,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:52</t>
+          <t>2026-06-21T14:46:27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -600,7 +600,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:52</t>
+          <t>2026-06-21T14:46:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:52</t>
+          <t>2026-06-21T14:46:27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -684,7 +684,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:52</t>
+          <t>2026-06-21T14:46:27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -726,7 +726,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:52</t>
+          <t>2026-06-21T14:46:27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -762,6 +762,53 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>{"department": "People", "email": "grace.hall@acme.co", "id": "e7", "is_active": true, "join_date": "2018-09-02", "manager_id": null, "name": "Grace Hall", "phone": "+1 415 555 0100", "role": "hr", "title": "HR Business Partner"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-21T14:50:21</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>e7</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>e8</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Vikram</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>vikram,m@test.com</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>{"department": "Engineering", "email": "vikram,m@test.com", "id": "e8", "is_active": true, "join_date": "2026-06-21", "manager_id": "e5", "name": "Vikram", "phone": "", "role": "employee", "title": "Engineering"}</t>
         </is>
       </c>
     </row>
@@ -776,7 +823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -819,7 +866,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:58</t>
+          <t>2026-06-21T14:46:33</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -851,7 +898,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:59</t>
+          <t>2026-06-21T14:46:34</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -883,7 +930,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:59</t>
+          <t>2026-06-21T14:46:34</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -915,7 +962,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:59</t>
+          <t>2026-06-21T14:46:34</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -947,7 +994,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:59</t>
+          <t>2026-06-21T14:46:34</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -979,7 +1026,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:59</t>
+          <t>2026-06-21T14:46:34</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1011,7 +1058,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-21T10:20:00</t>
+          <t>2026-06-21T14:46:35</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1043,7 +1090,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-21T10:20:00</t>
+          <t>2026-06-21T14:46:35</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1075,7 +1122,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-21T10:20:00</t>
+          <t>2026-06-21T14:46:35</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1107,7 +1154,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-21T10:20:00</t>
+          <t>2026-06-21T14:46:35</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1133,6 +1180,228 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>{"applied_on": "2026-06-07", "contact": "", "days": 2.0, "decided_by": "e7", "decision_reason": "", "employee_id": "e5", "end_date": "2026-06-25", "half_day": false, "handover": "Elena covers escalations", "id": "r10", "leave_type": "annual", "reason": "Long weekend", "start_date": "2026-06-24", "status": "approved"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-21T15:55:42</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>e1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>r11</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>e1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>{"applied_on": "2026-06-21", "contact": "", "days": 1.0, "decided_by": null, "decision_reason": "", "employee_id": "e1", "end_date": "2026-06-25", "half_day": false, "handover": "", "id": "r11", "leave_type": "annual", "reason": "Holiday", "start_date": "2026-06-25", "status": "pending"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-21T15:55:52</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>e1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>r12</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>e1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>{"applied_on": "2026-06-21", "contact": "", "days": 1.0, "decided_by": null, "decision_reason": "", "employee_id": "e1", "end_date": "2026-06-25", "half_day": false, "handover": "", "id": "r12", "leave_type": "annual", "reason": "Holiday", "start_date": "2026-06-25", "status": "pending"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-21T15:55:55</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>e1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>r13</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>e1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>{"applied_on": "2026-06-21", "contact": "", "days": 1.0, "decided_by": null, "decision_reason": "", "employee_id": "e1", "end_date": "2026-06-25", "half_day": false, "handover": "", "id": "r13", "leave_type": "annual", "reason": "Holiday", "start_date": "2026-06-25", "status": "pending"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-21T15:55:57</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>e1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>r14</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>e1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>{"applied_on": "2026-06-21", "contact": "", "days": 1.0, "decided_by": null, "decision_reason": "", "employee_id": "e1", "end_date": "2026-06-25", "half_day": false, "handover": "", "id": "r14", "leave_type": "annual", "reason": "Holiday", "start_date": "2026-06-25", "status": "pending"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-21T15:56:43</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>e5</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>r11</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>e1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>{"applied_on": "2026-06-21", "contact": "", "days": 1.0, "decided_by": "e5", "decision_reason": "", "employee_id": "e1", "end_date": "2026-06-25", "half_day": false, "handover": "", "id": "r11", "leave_type": "annual", "reason": "Holiday", "start_date": "2026-06-25", "status": "approved"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-21T15:56:52</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>e5</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>r13</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>e1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>{"applied_on": "2026-06-21", "contact": "", "days": 1.0, "decided_by": "e5", "decision_reason": "", "employee_id": "e1", "end_date": "2026-06-25", "half_day": false, "handover": "", "id": "r13", "leave_type": "annual", "reason": "Holiday", "start_date": "2026-06-25", "status": "approved"}</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1185,7 +1454,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-21T10:20:00</t>
+          <t>2026-06-21T14:46:35</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1205,14 +1474,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>{"action": "approved", "actor_id": "e5", "created_at": "2026-06-21 10:19:51.961653", "note": "", "request_id": "r1"}</t>
+          <t>{"action": "approved", "actor_id": "e5", "created_at": "2026-06-21 14:46:26.792792", "note": "", "request_id": "r1"}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-21T10:20:01</t>
+          <t>2026-06-21T14:46:35</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1232,14 +1501,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>{"action": "approved", "actor_id": "e5", "created_at": "2026-06-21 10:19:51.961653", "note": "", "request_id": "r2"}</t>
+          <t>{"action": "approved", "actor_id": "e5", "created_at": "2026-06-21 14:46:26.792792", "note": "", "request_id": "r2"}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-21T10:20:01</t>
+          <t>2026-06-21T14:46:36</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1264,14 +1533,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>{"action": "rejected", "actor_id": "e6", "created_at": "2026-06-21 10:19:51.961653", "note": "Quarter-end close. Please reschedule after the 10th.", "request_id": "r6"}</t>
+          <t>{"action": "rejected", "actor_id": "e6", "created_at": "2026-06-21 14:46:26.792792", "note": "Quarter-end close. Please reschedule after the 10th.", "request_id": "r6"}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-21T10:20:01</t>
+          <t>2026-06-21T14:46:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1291,14 +1560,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>{"action": "approved", "actor_id": "e6", "created_at": "2026-06-21 10:19:51.961653", "note": "", "request_id": "r7"}</t>
+          <t>{"action": "approved", "actor_id": "e6", "created_at": "2026-06-21 14:46:26.792792", "note": "", "request_id": "r7"}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-21T10:20:01</t>
+          <t>2026-06-21T14:46:36</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1318,7 +1587,61 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>{"action": "approved", "actor_id": "e7", "created_at": "2026-06-21 10:19:51.961653", "note": "", "request_id": "r10"}</t>
+          <t>{"action": "approved", "actor_id": "e7", "created_at": "2026-06-21 14:46:26.792792", "note": "", "request_id": "r10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-21T15:56:44</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>e5</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>r11</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>{"action": "approved", "actor_id": "e5", "created_at": "2026-06-21 15:56:43.374802", "note": "", "request_id": "r11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-21T15:56:52</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>e5</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>r13</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>{"action": "approved", "actor_id": "e5", "created_at": "2026-06-21 15:56:52.249982", "note": "", "request_id": "r13"}</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1376,7 +1699,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:52</t>
+          <t>2026-06-21T14:46:27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1406,7 +1729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:52</t>
+          <t>2026-06-21T14:46:27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1436,7 +1759,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:52</t>
+          <t>2026-06-21T14:46:27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1466,7 +1789,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:53</t>
+          <t>2026-06-21T14:46:28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1496,7 +1819,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:53</t>
+          <t>2026-06-21T14:46:28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1526,7 +1849,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:53</t>
+          <t>2026-06-21T14:46:28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1556,7 +1879,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:53</t>
+          <t>2026-06-21T14:46:28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1586,7 +1909,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:53</t>
+          <t>2026-06-21T14:46:28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1616,7 +1939,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:53</t>
+          <t>2026-06-21T14:46:28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1646,7 +1969,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:53</t>
+          <t>2026-06-21T14:46:28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1676,7 +1999,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:53</t>
+          <t>2026-06-21T14:46:28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1706,7 +2029,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:53</t>
+          <t>2026-06-21T14:46:29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1736,7 +2059,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:54</t>
+          <t>2026-06-21T14:46:29</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1766,7 +2089,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:54</t>
+          <t>2026-06-21T14:46:29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1796,7 +2119,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:54</t>
+          <t>2026-06-21T14:46:29</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1826,7 +2149,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:54</t>
+          <t>2026-06-21T14:46:29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1856,7 +2179,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:54</t>
+          <t>2026-06-21T14:46:29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1886,7 +2209,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:54</t>
+          <t>2026-06-21T14:46:29</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1916,7 +2239,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:54</t>
+          <t>2026-06-21T14:46:30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1946,7 +2269,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:54</t>
+          <t>2026-06-21T14:46:30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1976,7 +2299,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:55</t>
+          <t>2026-06-21T14:46:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2006,7 +2329,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:55</t>
+          <t>2026-06-21T14:46:30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2036,7 +2359,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:55</t>
+          <t>2026-06-21T14:46:30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2066,7 +2389,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:55</t>
+          <t>2026-06-21T14:46:30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2096,7 +2419,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:55</t>
+          <t>2026-06-21T14:46:31</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2126,7 +2449,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:56</t>
+          <t>2026-06-21T14:46:31</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2156,7 +2479,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:56</t>
+          <t>2026-06-21T14:46:31</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2186,7 +2509,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:56</t>
+          <t>2026-06-21T14:46:31</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2216,7 +2539,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:56</t>
+          <t>2026-06-21T14:46:31</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2246,7 +2569,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:56</t>
+          <t>2026-06-21T14:46:31</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2276,7 +2599,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:57</t>
+          <t>2026-06-21T14:46:31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2306,7 +2629,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:57</t>
+          <t>2026-06-21T14:46:32</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2336,7 +2659,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:57</t>
+          <t>2026-06-21T14:46:32</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2366,7 +2689,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:57</t>
+          <t>2026-06-21T14:46:32</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2396,7 +2719,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:57</t>
+          <t>2026-06-21T14:46:32</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2426,7 +2749,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:57</t>
+          <t>2026-06-21T14:46:32</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2456,7 +2779,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:57</t>
+          <t>2026-06-21T14:46:32</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2486,7 +2809,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:58</t>
+          <t>2026-06-21T14:46:33</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2516,7 +2839,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:58</t>
+          <t>2026-06-21T14:46:33</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2546,7 +2869,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:58</t>
+          <t>2026-06-21T14:46:33</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2576,7 +2899,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:58</t>
+          <t>2026-06-21T14:46:33</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2606,7 +2929,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-21T10:19:58</t>
+          <t>2026-06-21T14:46:33</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2630,6 +2953,216 @@
       <c r="G43" t="inlineStr">
         <is>
           <t>{"employee_id": "e7", "leave_type": "unpaid", "used": 0.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-06-21T14:50:20</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>e7</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>e8</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>{"employee_id": "e8", "leave_type": "annual", "used": 0.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-06-21T14:50:20</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>e7</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>e8</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>{"employee_id": "e8", "leave_type": "sick", "used": 0.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-06-21T14:50:20</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>e7</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>e8</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>casual</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>{"employee_id": "e8", "leave_type": "casual", "used": 0.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-06-21T14:50:20</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>e7</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>e8</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>earned</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>{"employee_id": "e8", "leave_type": "earned", "used": 0.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-06-21T14:50:20</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>e7</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>e8</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>maternity</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>{"employee_id": "e8", "leave_type": "maternity", "used": 0.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-21T14:50:21</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>e7</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>e8</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>unpaid</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>{"employee_id": "e8", "leave_type": "unpaid", "used": 0.0}</t>
         </is>
       </c>
     </row>
@@ -2687,7 +3220,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-21T10:20:02</t>
+          <t>2026-06-21T14:46:36</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2717,7 +3250,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-21T10:20:02</t>
+          <t>2026-06-21T14:46:37</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2747,7 +3280,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-21T10:20:02</t>
+          <t>2026-06-21T14:46:37</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2785,7 +3318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2823,7 +3356,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-21T10:20:02</t>
+          <t>2026-06-21T14:46:37</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2850,7 +3383,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-21T10:20:02</t>
+          <t>2026-06-21T14:46:37</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2877,7 +3410,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-21T10:20:02</t>
+          <t>2026-06-21T14:46:37</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2904,7 +3437,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-21T10:20:03</t>
+          <t>2026-06-21T14:46:37</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2925,6 +3458,230 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>{"actor_id": null, "created_at": "2026-05-02 00:00:00", "kind": "rejected", "text": "Elena Petrov declined Priya Nair's request"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-21T14:50:21</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>e7</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Grace Hall added Vikram</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>{"actor_id": "e7", "created_at": "2026-06-21 14:50:21.182644", "kind": "employee", "text": "Grace Hall added Vikram"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-21T15:55:42</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>e1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>request</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Maya Lin requested annual leave</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>{"actor_id": "e1", "created_at": "2026-06-21 15:55:41.997147", "kind": "request", "text": "Maya Lin requested annual leave"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-21T15:55:52</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>e1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>request</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Maya Lin requested annual leave</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>{"actor_id": "e1", "created_at": "2026-06-21 15:55:52.437718", "kind": "request", "text": "Maya Lin requested annual leave"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-21T15:55:55</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>e1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>request</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Maya Lin requested annual leave</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>{"actor_id": "e1", "created_at": "2026-06-21 15:55:55.157964", "kind": "request", "text": "Maya Lin requested annual leave"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-21T15:55:57</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>e1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>request</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Maya Lin requested annual leave</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>{"actor_id": "e1", "created_at": "2026-06-21 15:55:57.093619", "kind": "request", "text": "Maya Lin requested annual leave"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-21T15:56:43</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>e5</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>David Okafor approved Maya Lin's leave</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>{"actor_id": "e5", "created_at": "2026-06-21 15:56:43.378803", "kind": "approved", "text": "David Okafor approved Maya Lin's leave"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-21T15:56:52</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>e5</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>David Okafor approved Maya Lin's leave</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>{"actor_id": "e5", "created_at": "2026-06-21 15:56:52.252983", "kind": "approved", "text": "David Okafor approved Maya Lin's leave"}</t>
         </is>
       </c>
     </row>

--- a/database excel/daybook_records.xlsx
+++ b/database excel/daybook_records.xlsx
@@ -823,7 +823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1402,6 +1402,80 @@
       <c r="G17" t="inlineStr">
         <is>
           <t>{"applied_on": "2026-06-21", "contact": "", "days": 1.0, "decided_by": "e5", "decision_reason": "", "employee_id": "e1", "end_date": "2026-06-25", "half_day": false, "handover": "", "id": "r13", "leave_type": "annual", "reason": "Holiday", "start_date": "2026-06-25", "status": "approved"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-21T16:13:17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>e1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>r15</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>e1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>{"applied_on": "2026-06-21", "contact": "", "days": 2.0, "decided_by": null, "decision_reason": "", "employee_id": "e1", "end_date": "2026-06-25", "half_day": false, "handover": "", "id": "r15", "leave_type": "annual", "reason": "", "start_date": "2026-06-24", "status": "pending"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-21T16:13:51</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>e5</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>r12</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>e1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>{"applied_on": "2026-06-21", "contact": "", "days": 1.0, "decided_by": "e5", "decision_reason": "", "employee_id": "e1", "end_date": "2026-06-25", "half_day": false, "handover": "", "id": "r12", "leave_type": "annual", "reason": "Holiday", "start_date": "2026-06-25", "status": "approved"}</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1642,6 +1716,33 @@
       <c r="F8" t="inlineStr">
         <is>
           <t>{"action": "approved", "actor_id": "e5", "created_at": "2026-06-21 15:56:52.249982", "note": "", "request_id": "r13"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-21T16:13:51</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>e5</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>r12</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>{"action": "approved", "actor_id": "e5", "created_at": "2026-06-21 16:13:51.225972", "note": "", "request_id": "r12"}</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3685,6 +3786,70 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-21T16:13:17</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>e1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>request</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Maya Lin requested annual leave</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>{"actor_id": "e1", "created_at": "2026-06-21 16:13:17.344529", "kind": "request", "text": "Maya Lin requested annual leave"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-21T16:13:51</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>e5</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>David Okafor approved Maya Lin's leave</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>{"actor_id": "e5", "created_at": "2026-06-21 16:13:51.268750", "kind": "approved", "text": "David Okafor approved Maya Lin's leave"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
